--- a/data/controles_results/difmedias_dep_vars_2019.xlsx
+++ b/data/controles_results/difmedias_dep_vars_2019.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>835</t>
+    <t>832</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,7 +72,7 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>0.510</t>
+    <t>0.509</t>
   </si>
   <si>
     <t>(0.011)</t>
@@ -84,48 +84,48 @@
     <t>(0.002)</t>
   </si>
   <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>(0.001)</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (2) </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0.193</t>
+  </si>
+  <si>
+    <t>(0.014)</t>
+  </si>
+  <si>
+    <t>0.199</t>
+  </si>
+  <si>
     <t>0.006</t>
   </si>
   <si>
-    <t>(0.001)</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (2) </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0.193</t>
-  </si>
-  <si>
-    <t>(0.014)</t>
-  </si>
-  <si>
-    <t>0.200</t>
-  </si>
-  <si>
-    <t>0.007</t>
+    <t>(0.005)</t>
+  </si>
+  <si>
+    <t>0.675</t>
+  </si>
+  <si>
+    <t>(0.016)</t>
+  </si>
+  <si>
+    <t>0.010</t>
   </si>
   <si>
     <t>(0.006)</t>
   </si>
   <si>
-    <t>0.673</t>
-  </si>
-  <si>
-    <t>(0.016)</t>
-  </si>
-  <si>
-    <t>0.010</t>
-  </si>
-  <si>
-    <t>0.008</t>
-  </si>
-  <si>
     <t>896</t>
   </si>
   <si>
@@ -138,22 +138,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-0.014</t>
-  </si>
-  <si>
-    <t>-0.008</t>
+    <t>-0.015</t>
+  </si>
+  <si>
+    <t>-0.009</t>
   </si>
   <si>
     <t>0.006***</t>
   </si>
   <si>
-    <t>0.163***</t>
-  </si>
-  <si>
-    <t>-0.006</t>
-  </si>
-  <si>
-    <t>0.003</t>
+    <t>0.166***</t>
+  </si>
+  <si>
+    <t>-0.005</t>
+  </si>
+  <si>
+    <t>0.004</t>
   </si>
 </sst>
 </file>
@@ -513,7 +513,7 @@
         <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" t="s">
         <v>37</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
